--- a/Result/profitability/3360.xlsx
+++ b/Result/profitability/3360.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.31</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1375</v>
+        <v>-0.1075</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9575</v>
+        <v>3.915</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.11</v>
+        <v>-0.0975</v>
       </c>
       <c r="N3" t="n">
-        <v>4.26625</v>
+        <v>4.15375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.68</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.01499999999999999</v>
+        <v>0.02500000000000002</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5625</v>
+        <v>4.41375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1020,10 +1020,10 @@
         <v>-0.08</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01250000000000001</v>
+        <v>0.03750000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>4.75</v>
+        <v>4.56</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>-0.27</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001250000000000008</v>
+        <v>0.02625000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>4.84125</v>
+        <v>4.766249999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>0.06</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03125000000000001</v>
+        <v>0.01250000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>4.9975</v>
+        <v>4.8975</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1395,10 +1395,10 @@
         <v>0.51</v>
       </c>
       <c r="M8" t="n">
-        <v>0.07375000000000001</v>
+        <v>0.07625000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>5.1675</v>
+        <v>5.149999999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,135 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3360</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2937</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2847</v>
+      </c>
+      <c r="E75" t="n">
+        <v>90</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="G75" t="n">
+        <v>23</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.79%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-12</v>
+      </c>
+      <c r="J75" t="n">
+        <v>11</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.09624999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3.76625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.1400000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0434782608695653</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.111111111111111</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3304347826086956</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
